--- a/data_VK.xlsx
+++ b/data_VK.xlsx
@@ -1,15 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Институт\Магистратура\Интеллектуальные системы и технологии\vk_vektor\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69EE2D7B-0CD5-45F1-870A-2C9B910AF87B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -109,17 +120,17 @@
     <t>ogponcha</t>
   </si>
   <si>
-    <t>BSBO-10-26</t>
-  </si>
-  <si>
-    <t>BSBO-12-26</t>
+    <t>BSMO-11-26</t>
+  </si>
+  <si>
+    <t>BSMO-12-26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,17 +189,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -226,9 +245,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -260,9 +279,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -294,9 +331,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -469,11 +524,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,7 +539,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -492,7 +547,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -500,7 +555,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -508,7 +563,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -516,7 +571,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -524,7 +579,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -532,7 +587,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -540,7 +595,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -548,7 +603,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -556,7 +611,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -564,7 +619,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -572,7 +627,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -580,7 +635,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -588,7 +643,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -596,7 +651,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -604,7 +659,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -612,7 +667,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -620,7 +675,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -628,7 +683,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -636,7 +691,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -644,7 +699,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -652,7 +707,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -660,7 +715,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -668,7 +723,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -676,7 +731,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -684,7 +739,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -692,7 +747,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -700,7 +755,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
